--- a/03_BOM/SLT_4.xlsx
+++ b/03_BOM/SLT_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_Altium_Project\14_SLT\SLT_6U_SATELITE_EXP_HW\03_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C9DDFB-C630-40A4-A430-F67012E5EFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E342E2-4183-467E-83A3-E59CEAF02C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{FDFF0C48-B950-46AF-B276-FC36A3B1A940}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{FDFF0C48-B950-46AF-B276-FC36A3B1A940}"/>
   </bookViews>
   <sheets>
     <sheet name="SLT_4" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="430">
   <si>
     <t>Designator</t>
   </si>
@@ -1789,19 +1789,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F008F0B4-D5AC-477A-8015-3AD55C8BF0E3}">
   <dimension ref="A1:I95"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.88671875" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" customWidth="1"/>
+    <col min="1" max="1" width="33.85546875" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
     <col min="3" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" customWidth="1"/>
-    <col min="6" max="6" width="17.109375" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="69.21875" customWidth="1"/>
+    <col min="8" max="8" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="69.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>280</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>283</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>46</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>43</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>41</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>31</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>48</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>55</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>59</v>
       </c>
@@ -2394,7 +2394,9 @@
       <c r="E22" s="1">
         <v>10</v>
       </c>
-      <c r="F22" s="1"/>
+      <c r="F22" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="G22" s="1" t="s">
         <v>315</v>
       </c>
@@ -2405,7 +2407,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>63</v>
       </c>
@@ -2426,7 +2428,7 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>66</v>
       </c>
@@ -2442,7 +2444,9 @@
       <c r="E24" s="1">
         <v>3</v>
       </c>
-      <c r="F24" s="1"/>
+      <c r="F24" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="G24" s="1" t="s">
         <v>317</v>
       </c>
@@ -2453,7 +2457,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>69</v>
       </c>
@@ -2469,7 +2473,9 @@
       <c r="E25" s="1">
         <v>1</v>
       </c>
-      <c r="F25" s="1"/>
+      <c r="F25" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="G25" s="1" t="s">
         <v>317</v>
       </c>
@@ -2480,7 +2486,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>72</v>
       </c>
@@ -2496,7 +2502,9 @@
       <c r="E26" s="1">
         <v>5</v>
       </c>
-      <c r="F26" s="1"/>
+      <c r="F26" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="G26" s="1" t="s">
         <v>320</v>
       </c>
@@ -2507,7 +2515,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>76</v>
       </c>
@@ -2523,7 +2531,9 @@
       <c r="E27" s="1">
         <v>1</v>
       </c>
-      <c r="F27" s="1"/>
+      <c r="F27" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="G27" s="1" t="s">
         <v>317</v>
       </c>
@@ -2534,7 +2544,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>79</v>
       </c>
@@ -2550,7 +2560,9 @@
       <c r="E28" s="1">
         <v>1</v>
       </c>
-      <c r="F28" s="1"/>
+      <c r="F28" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="G28" s="1" t="s">
         <v>317</v>
       </c>
@@ -2561,7 +2573,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>82</v>
       </c>
@@ -2577,7 +2589,9 @@
       <c r="E29" s="1">
         <v>1</v>
       </c>
-      <c r="F29" s="1"/>
+      <c r="F29" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="G29" s="1" t="s">
         <v>324</v>
       </c>
@@ -2588,7 +2602,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>326</v>
       </c>
@@ -2604,7 +2618,9 @@
       <c r="E30" s="1">
         <v>3</v>
       </c>
-      <c r="F30" s="1"/>
+      <c r="F30" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="G30" s="1" t="s">
         <v>317</v>
       </c>
@@ -2615,7 +2631,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>87</v>
       </c>
@@ -2631,12 +2647,14 @@
       <c r="E31" s="1">
         <v>1</v>
       </c>
-      <c r="F31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>91</v>
       </c>
@@ -2652,7 +2670,9 @@
       <c r="E32" s="1">
         <v>1</v>
       </c>
-      <c r="F32" s="1"/>
+      <c r="F32" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="G32" s="1" t="s">
         <v>317</v>
       </c>
@@ -2663,7 +2683,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>95</v>
       </c>
@@ -2679,7 +2699,9 @@
       <c r="E33" s="1">
         <v>1</v>
       </c>
-      <c r="F33" s="1"/>
+      <c r="F33" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="G33" s="1" t="s">
         <v>330</v>
       </c>
@@ -2690,7 +2712,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>98</v>
       </c>
@@ -2706,7 +2728,9 @@
       <c r="E34" s="1">
         <v>1</v>
       </c>
-      <c r="F34" s="1"/>
+      <c r="F34" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="G34" s="1" t="s">
         <v>317</v>
       </c>
@@ -2717,7 +2741,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>101</v>
       </c>
@@ -2738,7 +2762,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>104</v>
       </c>
@@ -2765,7 +2789,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>108</v>
       </c>
@@ -2792,7 +2816,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>111</v>
       </c>
@@ -2821,7 +2845,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>115</v>
       </c>
@@ -2848,7 +2872,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>119</v>
       </c>
@@ -2875,7 +2899,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>122</v>
       </c>
@@ -2902,7 +2926,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>123</v>
       </c>
@@ -2929,7 +2953,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>127</v>
       </c>
@@ -2956,7 +2980,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>130</v>
       </c>
@@ -2983,7 +3007,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>176</v>
       </c>
@@ -3010,7 +3034,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>154</v>
       </c>
@@ -3037,7 +3061,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>358</v>
       </c>
@@ -3064,7 +3088,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>163</v>
       </c>
@@ -3091,7 +3115,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>172</v>
       </c>
@@ -3118,7 +3142,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>179</v>
       </c>
@@ -3145,7 +3169,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>152</v>
       </c>
@@ -3172,7 +3196,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>138</v>
       </c>
@@ -3199,7 +3223,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>140</v>
       </c>
@@ -3226,7 +3250,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>170</v>
       </c>
@@ -3253,7 +3277,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>165</v>
       </c>
@@ -3280,7 +3304,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>150</v>
       </c>
@@ -3307,7 +3331,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>144</v>
       </c>
@@ -3334,7 +3358,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>167</v>
       </c>
@@ -3361,7 +3385,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>147</v>
       </c>
@@ -3388,7 +3412,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>142</v>
       </c>
@@ -3415,7 +3439,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>157</v>
       </c>
@@ -3442,7 +3466,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>132</v>
       </c>
@@ -3469,7 +3493,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>136</v>
       </c>
@@ -3496,7 +3520,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>174</v>
       </c>
@@ -3523,7 +3547,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>159</v>
       </c>
@@ -3550,7 +3574,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>156</v>
       </c>
@@ -3577,7 +3601,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>391</v>
       </c>
@@ -3604,7 +3628,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>161</v>
       </c>
@@ -3631,7 +3655,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>181</v>
       </c>
@@ -3652,7 +3676,7 @@
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>184</v>
       </c>
@@ -3679,7 +3703,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>188</v>
       </c>
@@ -3708,7 +3732,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>191</v>
       </c>
@@ -3735,7 +3759,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>194</v>
       </c>
@@ -3762,7 +3786,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>197</v>
       </c>
@@ -3789,7 +3813,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>200</v>
       </c>
@@ -3816,7 +3840,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>203</v>
       </c>
@@ -3843,7 +3867,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>206</v>
       </c>
@@ -3870,7 +3894,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>210</v>
       </c>
@@ -3897,7 +3921,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>214</v>
       </c>
@@ -3924,7 +3948,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>218</v>
       </c>
@@ -3951,7 +3975,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>221</v>
       </c>
@@ -3978,7 +4002,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>224</v>
       </c>
@@ -3999,7 +4023,7 @@
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>227</v>
       </c>
@@ -4026,7 +4050,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>231</v>
       </c>
@@ -4053,7 +4077,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>234</v>
       </c>
@@ -4080,7 +4104,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>236</v>
       </c>
@@ -4107,7 +4131,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>239</v>
       </c>
@@ -4134,7 +4158,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>241</v>
       </c>
@@ -4161,7 +4185,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>245</v>
       </c>
@@ -4188,7 +4212,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>249</v>
       </c>
@@ -4215,7 +4239,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>253</v>
       </c>
@@ -4242,7 +4266,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>256</v>
       </c>
@@ -4269,7 +4293,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>260</v>
       </c>
@@ -4296,7 +4320,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>264</v>
       </c>
@@ -4323,7 +4347,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>268</v>
       </c>

--- a/03_BOM/SLT_4.xlsx
+++ b/03_BOM/SLT_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_Altium_Project\14_SLT\SLT_6U_SATELITE_EXP_HW\03_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E342E2-4183-467E-83A3-E59CEAF02C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBCA8EE-B8BF-4295-85F5-9C6C73519A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{FDFF0C48-B950-46AF-B276-FC36A3B1A940}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{FDFF0C48-B950-46AF-B276-FC36A3B1A940}"/>
   </bookViews>
   <sheets>
     <sheet name="SLT_4" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="430">
   <si>
     <t>Designator</t>
   </si>
@@ -1789,19 +1789,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F008F0B4-D5AC-477A-8015-3AD55C8BF0E3}">
   <dimension ref="A1:I95"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.85546875" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.88671875" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" customWidth="1"/>
     <col min="3" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="69.28515625" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="69.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>280</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>283</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>46</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>43</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>41</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>31</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>48</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>55</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>59</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>63</v>
       </c>
@@ -2428,7 +2428,7 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>66</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>69</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>72</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>76</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>79</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>82</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>326</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>87</v>
       </c>
@@ -2654,7 +2654,7 @@
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>91</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>95</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>98</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>101</v>
       </c>
@@ -2762,7 +2762,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>104</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>108</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>111</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>115</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>119</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>122</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>123</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>127</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>130</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>176</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>154</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>358</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>163</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>172</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>179</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>152</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>138</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>140</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>170</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>165</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>150</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>144</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>167</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>147</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>142</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>157</v>
       </c>
@@ -3466,7 +3466,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>132</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>136</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>174</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>159</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>156</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>391</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>161</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>181</v>
       </c>
@@ -3676,7 +3676,7 @@
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>184</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>188</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>191</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>194</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>197</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>200</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>203</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>206</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>210</v>
       </c>
@@ -3910,7 +3910,9 @@
       <c r="E78" s="1">
         <v>2</v>
       </c>
-      <c r="F78" s="1"/>
+      <c r="F78" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="G78" s="1" t="s">
         <v>398</v>
       </c>
@@ -3921,7 +3923,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>214</v>
       </c>
@@ -3948,7 +3950,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>218</v>
       </c>
@@ -3975,7 +3977,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>221</v>
       </c>
@@ -4002,7 +4004,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>224</v>
       </c>
@@ -4023,7 +4025,7 @@
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>227</v>
       </c>
@@ -4050,7 +4052,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>231</v>
       </c>
@@ -4077,7 +4079,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>234</v>
       </c>
@@ -4104,7 +4106,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>236</v>
       </c>
@@ -4131,7 +4133,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>239</v>
       </c>
@@ -4158,7 +4160,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>241</v>
       </c>
@@ -4185,7 +4187,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>245</v>
       </c>
@@ -4212,7 +4214,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>249</v>
       </c>
@@ -4239,7 +4241,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>253</v>
       </c>
@@ -4266,7 +4268,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>256</v>
       </c>
@@ -4293,7 +4295,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>260</v>
       </c>
@@ -4320,7 +4322,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>264</v>
       </c>
@@ -4347,7 +4349,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>268</v>
       </c>

--- a/03_BOM/SLT_4.xlsx
+++ b/03_BOM/SLT_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_Altium_Project\14_SLT\SLT_6U_SATELITE_EXP_HW\03_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBCA8EE-B8BF-4295-85F5-9C6C73519A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D7ED9D-6373-4F9D-B638-E29F344A954E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{FDFF0C48-B950-46AF-B276-FC36A3B1A940}"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21600" xr2:uid="{FDFF0C48-B950-46AF-B276-FC36A3B1A940}"/>
   </bookViews>
   <sheets>
     <sheet name="SLT_4" sheetId="1" r:id="rId1"/>
@@ -1789,19 +1789,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F008F0B4-D5AC-477A-8015-3AD55C8BF0E3}">
   <dimension ref="A1:I95"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.88671875" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" customWidth="1"/>
+    <col min="1" max="1" width="33.85546875" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
     <col min="3" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" customWidth="1"/>
-    <col min="6" max="6" width="17.109375" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="69.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>280</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>283</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>46</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>43</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>41</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>31</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>48</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>55</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>59</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>63</v>
       </c>
@@ -2428,7 +2428,7 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>66</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>69</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>72</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>76</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>79</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>82</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>326</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>87</v>
       </c>
@@ -2654,7 +2654,7 @@
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>91</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>95</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>98</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>101</v>
       </c>
@@ -2762,7 +2762,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>104</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>108</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>111</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>115</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>119</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>122</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>123</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>127</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>130</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>176</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>154</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>358</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>163</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>172</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>179</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>152</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>138</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>140</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>170</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>165</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>150</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>144</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>167</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>147</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>142</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>157</v>
       </c>
@@ -3466,7 +3466,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>132</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>136</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>174</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>159</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>156</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>391</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>161</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>181</v>
       </c>
@@ -3676,7 +3676,7 @@
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>184</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>188</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>191</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>194</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>197</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>200</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>203</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>206</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>210</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>214</v>
       </c>
@@ -3950,7 +3950,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>218</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>221</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>224</v>
       </c>
@@ -4025,7 +4025,7 @@
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>227</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>231</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>234</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>236</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>239</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>241</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>245</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>249</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>253</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>256</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>260</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>264</v>
       </c>
@@ -4349,7 +4349,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>268</v>
       </c>
